--- a/Modificaciones solicitadas.xlsx
+++ b/Modificaciones solicitadas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Xamarin\RowingApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{969722BA-1B44-441F-94CB-1AE30023DF77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42E12694-C233-4212-BDA2-91B033CA86C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{2D167E44-E563-4DF9-9CAD-3636B941BCB8}"/>
   </bookViews>
@@ -599,23 +599,25 @@
       <c r="D7" s="5"/>
       <c r="E7" s="3"/>
     </row>
-    <row r="8" spans="1:5" ht="51" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
         <v>44512</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8" s="6"/>
+        <v>7</v>
+      </c>
+      <c r="C8" s="8">
+        <v>44513</v>
+      </c>
       <c r="D8" s="5"/>
       <c r="E8" s="3"/>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" ht="51" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
         <v>44512</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C9" s="6"/>
       <c r="D9" s="5"/>

--- a/Modificaciones solicitadas.xlsx
+++ b/Modificaciones solicitadas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Xamarin\RowingApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42E12694-C233-4212-BDA2-91B033CA86C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81A50C3E-5D6D-4132-9982-B6B3B2466C29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{2D167E44-E563-4DF9-9CAD-3636B941BCB8}"/>
   </bookViews>
@@ -619,7 +619,9 @@
       <c r="B9" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="6"/>
+      <c r="C9" s="8">
+        <v>44520</v>
+      </c>
       <c r="D9" s="5"/>
       <c r="E9" s="3"/>
     </row>

--- a/Modificaciones solicitadas.xlsx
+++ b/Modificaciones solicitadas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Xamarin\RowingApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81A50C3E-5D6D-4132-9982-B6B3B2466C29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EE33721-D59D-4A52-874D-2F286E4E138D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{2D167E44-E563-4DF9-9CAD-3636B941BCB8}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="15">
   <si>
     <t>Fecha</t>
   </si>
@@ -76,6 +76,9 @@
   </si>
   <si>
     <t>Opción de Menú Medidores. Que pida ASTICKET, muestre datos (terminal, nombre, dirección, numeración, localidad, cliente y teléfono)  y luego se pueda cargar campos (SerieMedidorColocado, Precinto, CajaDAE, Observaciones, Lindero1, Lindero2) y se puedan cargar fotos (Nro Medidor Colocado, Estado de medidor retirado, Nro de precinto, Nro de tapa o caja, Lindero1 y Lindero2)</t>
+  </si>
+  <si>
+    <t>23/11/2021 V.4</t>
   </si>
 </sst>
 </file>
@@ -530,7 +533,9 @@
         <v>44502</v>
       </c>
       <c r="D2" s="5"/>
-      <c r="E2" s="3"/>
+      <c r="E2" s="8" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
@@ -545,7 +550,9 @@
       <c r="D3" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="3"/>
+      <c r="E3" s="8" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
@@ -558,7 +565,9 @@
         <v>44511</v>
       </c>
       <c r="D4" s="5"/>
-      <c r="E4" s="3"/>
+      <c r="E4" s="8" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
@@ -571,7 +580,9 @@
         <v>44512</v>
       </c>
       <c r="D5" s="5"/>
-      <c r="E5" s="3"/>
+      <c r="E5" s="8" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
@@ -584,7 +595,9 @@
         <v>44512</v>
       </c>
       <c r="D6" s="5"/>
-      <c r="E6" s="3"/>
+      <c r="E6" s="8" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
@@ -597,7 +610,9 @@
         <v>44512</v>
       </c>
       <c r="D7" s="5"/>
-      <c r="E7" s="3"/>
+      <c r="E7" s="8" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
@@ -610,7 +625,9 @@
         <v>44513</v>
       </c>
       <c r="D8" s="5"/>
-      <c r="E8" s="3"/>
+      <c r="E8" s="8" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="9" spans="1:5" ht="51" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
@@ -623,7 +640,9 @@
         <v>44520</v>
       </c>
       <c r="D9" s="5"/>
-      <c r="E9" s="3"/>
+      <c r="E9" s="8" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="3"/>

--- a/Modificaciones solicitadas.xlsx
+++ b/Modificaciones solicitadas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Xamarin\RowingApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EE33721-D59D-4A52-874D-2F286E4E138D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4805B674-BC42-4FC5-B5BE-51E6C6349488}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{2D167E44-E563-4DF9-9CAD-3636B941BCB8}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="23">
   <si>
     <t>Fecha</t>
   </si>
@@ -79,6 +79,30 @@
   </si>
   <si>
     <t>23/11/2021 V.4</t>
+  </si>
+  <si>
+    <t>Condición de Login, únicamente campo HabilitaApp</t>
+  </si>
+  <si>
+    <t>Agregar al Usuario Logueado los campos Código Grupo y Código Causante</t>
+  </si>
+  <si>
+    <t>Inspecciones. Es un nuevo menú. Esperar tablas.</t>
+  </si>
+  <si>
+    <t>En legajo a buscar también agregar PPC</t>
+  </si>
+  <si>
+    <t>Reclamos. Es un nuevo menú. Al entrar se ven los reclamos cargados en el día. Se debe poder cargar uno nuevo y volver a la pantalla anterior. Este menú es sólo para HabilitaReclamos=true. También se debe poder hacer un pedido de materiales. Los catálogos salen de la tabla catálogos que tengan el campo Verenreclamoapp en 1.</t>
+  </si>
+  <si>
+    <t>Las obras a mostrar deben ser del módulo del usuario logueado</t>
+  </si>
+  <si>
+    <t>En listado de materiales de un legajo agregar PPC a PPR. Sacar fecha distinto a null de la condición (se deben mostrar también). Agregar el campo Ultima fecha de entrega.</t>
+  </si>
+  <si>
+    <t>Sacar la condición SUPERVISORE &lt;&gt; Sin Asignar delas Obras que se traen</t>
   </si>
 </sst>
 </file>
@@ -494,7 +518,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F4F8DBC-1A7E-4CD8-B2CF-503AC5EB2B70}">
-  <dimension ref="A1:E45"/>
+  <dimension ref="A1:E46"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="10.199999999999999" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.6640625" style="7" customWidth="1"/>
@@ -645,57 +669,97 @@
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="3"/>
-      <c r="B10" s="4"/>
-      <c r="C10" s="6"/>
+      <c r="A10" s="3">
+        <v>44538</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="3">
+        <v>44538</v>
+      </c>
       <c r="D10" s="5"/>
       <c r="E10" s="3"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="3"/>
-      <c r="B11" s="4"/>
-      <c r="C11" s="6"/>
+      <c r="A11" s="3">
+        <v>44538</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="3">
+        <v>44538</v>
+      </c>
       <c r="D11" s="5"/>
       <c r="E11" s="3"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="3"/>
-      <c r="B12" s="4"/>
-      <c r="C12" s="6"/>
+      <c r="A12" s="3">
+        <v>44538</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" s="3">
+        <v>44538</v>
+      </c>
       <c r="D12" s="5"/>
       <c r="E12" s="3"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="3"/>
-      <c r="B13" s="4"/>
-      <c r="C13" s="6"/>
+      <c r="A13" s="3">
+        <v>44538</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13" s="3">
+        <v>44538</v>
+      </c>
       <c r="D13" s="5"/>
       <c r="E13" s="3"/>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="3"/>
-      <c r="B14" s="4"/>
+    <row r="14" spans="1:5" ht="40.799999999999997" x14ac:dyDescent="0.3">
+      <c r="A14" s="3">
+        <v>44538</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>19</v>
+      </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5"/>
       <c r="E14" s="3"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="3"/>
-      <c r="B15" s="4"/>
+      <c r="A15" s="3">
+        <v>44538</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>17</v>
+      </c>
       <c r="C15" s="6"/>
       <c r="D15" s="5"/>
       <c r="E15" s="3"/>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="3"/>
-      <c r="B16" s="4"/>
+    <row r="16" spans="1:5" ht="30.6" x14ac:dyDescent="0.3">
+      <c r="A16" s="3">
+        <v>44538</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>21</v>
+      </c>
       <c r="C16" s="6"/>
       <c r="D16" s="5"/>
       <c r="E16" s="3"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="3"/>
-      <c r="B17" s="4"/>
+      <c r="A17" s="3">
+        <v>44538</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>18</v>
+      </c>
       <c r="C17" s="6"/>
       <c r="D17" s="5"/>
       <c r="E17" s="3"/>
@@ -896,6 +960,13 @@
       <c r="D45" s="5"/>
       <c r="E45" s="3"/>
     </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A46" s="3"/>
+      <c r="B46" s="4"/>
+      <c r="C46" s="6"/>
+      <c r="D46" s="5"/>
+      <c r="E46" s="3"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>

--- a/Modificaciones solicitadas.xlsx
+++ b/Modificaciones solicitadas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Xamarin\RowingApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4805B674-BC42-4FC5-B5BE-51E6C6349488}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD6DD124-A25C-4D28-9DB7-5DE10FA5D171}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{2D167E44-E563-4DF9-9CAD-3636B941BCB8}"/>
   </bookViews>
@@ -131,7 +131,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -147,6 +147,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -178,7 +184,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -202,6 +208,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -675,7 +684,7 @@
       <c r="B10" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C10" s="9">
         <v>44538</v>
       </c>
       <c r="D10" s="5"/>
@@ -688,7 +697,7 @@
       <c r="B11" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="3">
+      <c r="C11" s="9">
         <v>44538</v>
       </c>
       <c r="D11" s="5"/>
@@ -701,7 +710,7 @@
       <c r="B12" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C12" s="3">
+      <c r="C12" s="9">
         <v>44538</v>
       </c>
       <c r="D12" s="5"/>
@@ -714,20 +723,22 @@
       <c r="B13" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C13" s="3">
+      <c r="C13" s="9">
         <v>44538</v>
       </c>
       <c r="D13" s="5"/>
       <c r="E13" s="3"/>
     </row>
-    <row r="14" spans="1:5" ht="40.799999999999997" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" ht="30.6" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
         <v>44538</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C14" s="6"/>
+        <v>21</v>
+      </c>
+      <c r="C14" s="9">
+        <v>44539</v>
+      </c>
       <c r="D14" s="5"/>
       <c r="E14" s="3"/>
     </row>
@@ -736,18 +747,20 @@
         <v>44538</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C15" s="6"/>
+        <v>18</v>
+      </c>
+      <c r="C15" s="9">
+        <v>44539</v>
+      </c>
       <c r="D15" s="5"/>
       <c r="E15" s="3"/>
     </row>
-    <row r="16" spans="1:5" ht="30.6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" ht="40.799999999999997" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
         <v>44538</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="5"/>
@@ -758,7 +771,7 @@
         <v>44538</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C17" s="6"/>
       <c r="D17" s="5"/>

--- a/Modificaciones solicitadas.xlsx
+++ b/Modificaciones solicitadas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Xamarin\RowingApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD6DD124-A25C-4D28-9DB7-5DE10FA5D171}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00CE3BAA-BE3E-41F7-89E8-705EBDAF2EA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{2D167E44-E563-4DF9-9CAD-3636B941BCB8}"/>
   </bookViews>
@@ -184,7 +184,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -212,6 +212,9 @@
     </xf>
     <xf numFmtId="14" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -762,7 +765,7 @@
       <c r="B16" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C16" s="6"/>
+      <c r="C16" s="10"/>
       <c r="D16" s="5"/>
       <c r="E16" s="3"/>
     </row>

--- a/Modificaciones solicitadas.xlsx
+++ b/Modificaciones solicitadas.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24701"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Xamarin\RowingApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00CE3BAA-BE3E-41F7-89E8-705EBDAF2EA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FA905B2-4C77-408C-BD11-34F063C7602D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{2D167E44-E563-4DF9-9CAD-3636B941BCB8}"/>
   </bookViews>
@@ -213,7 +213,7 @@
     <xf numFmtId="14" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -765,7 +765,9 @@
       <c r="B16" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C16" s="10"/>
+      <c r="C16" s="10">
+        <v>44540</v>
+      </c>
       <c r="D16" s="5"/>
       <c r="E16" s="3"/>
     </row>

--- a/Modificaciones solicitadas.xlsx
+++ b/Modificaciones solicitadas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Xamarin\RowingApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FA905B2-4C77-408C-BD11-34F063C7602D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8779123D-043A-4956-9AC0-12693BC1E0EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{2D167E44-E563-4DF9-9CAD-3636B941BCB8}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="24">
   <si>
     <t>Fecha</t>
   </si>
@@ -93,9 +93,6 @@
     <t>En legajo a buscar también agregar PPC</t>
   </si>
   <si>
-    <t>Reclamos. Es un nuevo menú. Al entrar se ven los reclamos cargados en el día. Se debe poder cargar uno nuevo y volver a la pantalla anterior. Este menú es sólo para HabilitaReclamos=true. También se debe poder hacer un pedido de materiales. Los catálogos salen de la tabla catálogos que tengan el campo Verenreclamoapp en 1.</t>
-  </si>
-  <si>
     <t>Las obras a mostrar deben ser del módulo del usuario logueado</t>
   </si>
   <si>
@@ -103,6 +100,12 @@
   </si>
   <si>
     <t>Sacar la condición SUPERVISORE &lt;&gt; Sin Asignar delas Obras que se traen</t>
+  </si>
+  <si>
+    <t>13/12/2021 V.5</t>
+  </si>
+  <si>
+    <t>Reclamos. Es un nuevo menú. Al entrar se ven los reclamos de la Obra. Se debe poder cargar uno nuevo y volver a la pantalla anterior. Este menú es sólo para HabilitaReclamos=true. También se debe poder hacer un pedido de materiales. Los catálogos salen de la tabla catálogos que tengan el campo Verenreclamoapp en 1.</t>
   </si>
 </sst>
 </file>
@@ -131,7 +134,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -153,6 +156,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -184,7 +193,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -215,6 +224,12 @@
     </xf>
     <xf numFmtId="14" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -691,7 +706,9 @@
         <v>44538</v>
       </c>
       <c r="D10" s="5"/>
-      <c r="E10" s="3"/>
+      <c r="E10" s="9" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
@@ -704,46 +721,54 @@
         <v>44538</v>
       </c>
       <c r="D11" s="5"/>
-      <c r="E11" s="3"/>
+      <c r="E11" s="9" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
         <v>44538</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C12" s="9">
         <v>44538</v>
       </c>
       <c r="D12" s="5"/>
-      <c r="E12" s="3"/>
+      <c r="E12" s="9" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="3">
         <v>44538</v>
       </c>
       <c r="B13" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C13" s="9">
+        <v>44538</v>
+      </c>
+      <c r="D13" s="5"/>
+      <c r="E13" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C13" s="9">
-        <v>44538</v>
-      </c>
-      <c r="D13" s="5"/>
-      <c r="E13" s="3"/>
     </row>
     <row r="14" spans="1:5" ht="30.6" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
         <v>44538</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C14" s="9">
         <v>44539</v>
       </c>
       <c r="D14" s="5"/>
-      <c r="E14" s="3"/>
+      <c r="E14" s="9" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
@@ -756,26 +781,30 @@
         <v>44539</v>
       </c>
       <c r="D15" s="5"/>
-      <c r="E15" s="3"/>
+      <c r="E15" s="9" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="16" spans="1:5" ht="40.799999999999997" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
         <v>44538</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C16" s="10">
-        <v>44540</v>
+        <v>44543</v>
       </c>
       <c r="D16" s="5"/>
-      <c r="E16" s="3"/>
+      <c r="E16" s="9" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="3">
-        <v>44538</v>
-      </c>
-      <c r="B17" s="4" t="s">
+      <c r="A17" s="11">
+        <v>44538</v>
+      </c>
+      <c r="B17" s="12" t="s">
         <v>17</v>
       </c>
       <c r="C17" s="6"/>

--- a/Modificaciones solicitadas.xlsx
+++ b/Modificaciones solicitadas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Xamarin\RowingApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8779123D-043A-4956-9AC0-12693BC1E0EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13B00E9A-86B4-4BF1-A301-BA6815EF3731}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{2D167E44-E563-4DF9-9CAD-3636B941BCB8}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="25">
   <si>
     <t>Fecha</t>
   </si>
@@ -106,6 +106,9 @@
   </si>
   <si>
     <t>Reclamos. Es un nuevo menú. Al entrar se ven los reclamos de la Obra. Se debe poder cargar uno nuevo y volver a la pantalla anterior. Este menú es sólo para HabilitaReclamos=true. También se debe poder hacer un pedido de materiales. Los catálogos salen de la tabla catálogos que tengan el campo Verenreclamoapp en 1.</t>
+  </si>
+  <si>
+    <t>Poner menu Reclamos y sacarlo de Obras. Que se pueda elegir la Obra (serán 2, en Tabla Obras las que tienen HabilitaReclamosAPP = 1 y módulo = al del usuario logueado)</t>
   </si>
 </sst>
 </file>
@@ -811,9 +814,13 @@
       <c r="D17" s="5"/>
       <c r="E17" s="3"/>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="3"/>
-      <c r="B18" s="4"/>
+    <row r="18" spans="1:5" ht="30.6" x14ac:dyDescent="0.3">
+      <c r="A18" s="3">
+        <v>44545</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>24</v>
+      </c>
       <c r="C18" s="6"/>
       <c r="D18" s="5"/>
       <c r="E18" s="3"/>

--- a/Modificaciones solicitadas.xlsx
+++ b/Modificaciones solicitadas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Xamarin\RowingApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13B00E9A-86B4-4BF1-A301-BA6815EF3731}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{231CB6F1-8FAE-45BD-9717-0BC2FC884140}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{2D167E44-E563-4DF9-9CAD-3636B941BCB8}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="26">
   <si>
     <t>Fecha</t>
   </si>
@@ -109,6 +109,9 @@
   </si>
   <si>
     <t>Poner menu Reclamos y sacarlo de Obras. Que se pueda elegir la Obra (serán 2, en Tabla Obras las que tienen HabilitaReclamosAPP = 1 y módulo = al del usuario logueado)</t>
+  </si>
+  <si>
+    <t>20/12/2021 V.6</t>
   </si>
 </sst>
 </file>
@@ -821,9 +824,13 @@
       <c r="B18" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C18" s="6"/>
+      <c r="C18" s="10">
+        <v>44546</v>
+      </c>
       <c r="D18" s="5"/>
-      <c r="E18" s="3"/>
+      <c r="E18" s="9" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="3"/>

--- a/Modificaciones solicitadas.xlsx
+++ b/Modificaciones solicitadas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Xamarin\RowingApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{231CB6F1-8FAE-45BD-9717-0BC2FC884140}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CBEAA16-7F52-4BCF-A153-79D595FD089E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{2D167E44-E563-4DF9-9CAD-3636B941BCB8}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="28">
   <si>
     <t>Fecha</t>
   </si>
@@ -112,6 +112,12 @@
   </si>
   <si>
     <t>20/12/2021 V.6</t>
+  </si>
+  <si>
+    <t>Cuando hay una sola foto no la pueden borrar</t>
+  </si>
+  <si>
+    <t>Poder subir fotos de la galería</t>
   </si>
 </sst>
 </file>
@@ -833,15 +839,23 @@
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="3"/>
-      <c r="B19" s="4"/>
+      <c r="A19" s="3">
+        <v>44550</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>26</v>
+      </c>
       <c r="C19" s="6"/>
       <c r="D19" s="5"/>
       <c r="E19" s="3"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" s="3"/>
-      <c r="B20" s="4"/>
+      <c r="A20" s="3">
+        <v>44550</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>27</v>
+      </c>
       <c r="C20" s="6"/>
       <c r="D20" s="5"/>
       <c r="E20" s="3"/>

--- a/Modificaciones solicitadas.xlsx
+++ b/Modificaciones solicitadas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Xamarin\RowingApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CBEAA16-7F52-4BCF-A153-79D595FD089E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75748FAA-5471-4388-AC7B-03B719E2AB34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{2D167E44-E563-4DF9-9CAD-3636B941BCB8}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="29">
   <si>
     <t>Fecha</t>
   </si>
@@ -118,6 +118,9 @@
   </si>
   <si>
     <t>Poder subir fotos de la galería</t>
+  </si>
+  <si>
+    <t>Agregar en Obras como opción de foto "Vereda conforme". Ponerlo antes de "Finalización del trabajo"</t>
   </si>
 </sst>
 </file>
@@ -845,7 +848,9 @@
       <c r="B19" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C19" s="6"/>
+      <c r="C19" s="10">
+        <v>44550</v>
+      </c>
       <c r="D19" s="5"/>
       <c r="E19" s="3"/>
     </row>
@@ -856,14 +861,22 @@
       <c r="B20" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="6"/>
+      <c r="C20" s="10">
+        <v>44550</v>
+      </c>
       <c r="D20" s="5"/>
       <c r="E20" s="3"/>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="3"/>
-      <c r="B21" s="4"/>
-      <c r="C21" s="6"/>
+    <row r="21" spans="1:5" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A21" s="3">
+        <v>44552</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C21" s="10">
+        <v>44552</v>
+      </c>
       <c r="D21" s="5"/>
       <c r="E21" s="3"/>
     </row>

--- a/Modificaciones solicitadas.xlsx
+++ b/Modificaciones solicitadas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Xamarin\RowingApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75748FAA-5471-4388-AC7B-03B719E2AB34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16D29D31-7A7E-404E-ADDA-E64DAED2F15D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{2D167E44-E563-4DF9-9CAD-3636B941BCB8}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="30">
   <si>
     <t>Fecha</t>
   </si>
@@ -121,6 +121,9 @@
   </si>
   <si>
     <t>Agregar en Obras como opción de foto "Vereda conforme". Ponerlo antes de "Finalización del trabajo"</t>
+  </si>
+  <si>
+    <t>27/12/2021 V.7</t>
   </si>
 </sst>
 </file>
@@ -852,7 +855,9 @@
         <v>44550</v>
       </c>
       <c r="D19" s="5"/>
-      <c r="E19" s="3"/>
+      <c r="E19" s="9" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="3">
@@ -865,7 +870,9 @@
         <v>44550</v>
       </c>
       <c r="D20" s="5"/>
-      <c r="E20" s="3"/>
+      <c r="E20" s="9" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="21" spans="1:5" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A21" s="3">
@@ -878,7 +885,9 @@
         <v>44552</v>
       </c>
       <c r="D21" s="5"/>
-      <c r="E21" s="3"/>
+      <c r="E21" s="9" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="3"/>
